--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487830_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487830_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6047</v>
+        <v>12.5334</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4421</v>
+        <v>12.4002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1626</v>
+        <v>0.1332</v>
       </c>
       <c r="G2" t="n">
         <v>8.2067</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1391</v>
+        <v>1.0678</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1149</v>
+        <v>1.073</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0242</v>
+        <v>-0.0052</v>
       </c>
       <c r="V2" t="n">
         <v>2.2183</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6713</v>
+        <v>6.9322</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0389</v>
+        <v>7.2999</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3677</v>
@@ -688,10 +688,10 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9225</v>
+        <v>1.1835</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.7887</v>
       </c>
       <c r="U3" t="n">
         <v>0.3948</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4241</v>
+        <v>3.5325</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7461</v>
+        <v>3.4417</v>
       </c>
       <c r="F4" t="n">
-        <v>0.678</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>1.5432</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3951</v>
+        <v>1.5035</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1522</v>
+        <v>0.8478</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2429</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3467</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5939</v>
+        <v>1.0789</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7748</v>
+        <v>2.0544</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1809</v>
+        <v>-0.9754</v>
       </c>
       <c r="G5" t="n">
         <v>1.9492</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.137</v>
+        <v>0.6221</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4658</v>
+        <v>0.7453</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3288</v>
+        <v>-0.1233</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2843</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1153</v>
+        <v>0.4971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5896</v>
+        <v>1.3022</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7049</v>
+        <v>-0.8051</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.322</v>
+        <v>2.4324</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4162</v>
+        <v>2.9189</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7382</v>
+        <v>-0.4866</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4441</v>
+        <v>3.0489</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1919</v>
+        <v>2.9314</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.636</v>
+        <v>0.1176</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8779</v>
+        <v>-0.6166</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2243</v>
+        <v>-0.0124</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1022</v>
+        <v>-0.6041</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
         <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3771</v>
+        <v>-0.3952</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1338</v>
+        <v>0.2096</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2433</v>
+        <v>-0.6047</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1675</v>
+        <v>-0.7076</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>-0.7076</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2572</v>
+        <v>0.1391</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6359</v>
+        <v>0.7854</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8932</v>
+        <v>-0.6462</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4324</v>
+        <v>-1.322</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9189</v>
+        <v>0.4162</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4866</v>
+        <v>-1.7382</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0489</v>
+        <v>-0.4441</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9314</v>
+        <v>0.1919</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1176</v>
+        <v>-0.636</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6166</v>
+        <v>-0.8779</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0124</v>
+        <v>0.2243</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6041</v>
+        <v>-1.1022</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1495</v>
+        <v>-0.1226</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4567</v>
+        <v>0.0619</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6928</v>
+        <v>-0.1846</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5384</v>
+        <v>-0.4248</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8462</v>
+        <v>-0.6738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3077</v>
+        <v>0.249</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2273</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6381</v>
+        <v>0.7517</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2048</v>
+        <v>0.3772</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4332</v>
+        <v>0.3745</v>
       </c>
       <c r="V8" t="n">
         <v>1.0508</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2635</v>
+        <v>-2.0096</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2468</v>
+        <v>-1.1397</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0167</v>
+        <v>-0.8699</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8798</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1756</v>
+        <v>-0.9217</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0451</v>
+        <v>-0.8983</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8955</v>
+        <v>-2.0721</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.679</v>
+        <v>-2.1199</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2165</v>
+        <v>0.0477</v>
       </c>
       <c r="G10" t="n">
         <v>0.8826000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0726</v>
+        <v>-0.2492</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7829</v>
+        <v>-0.2238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2896</v>
+        <v>-0.0254</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1782</v>
+        <v>-3.8563</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.556</v>
+        <v>-3.1459</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6223</v>
+        <v>-0.7103</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1098</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1735</v>
+        <v>0.1484</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1272</v>
+        <v>0.5372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3007</v>
+        <v>-0.3888</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.0459</v>
+        <v>16.3504</v>
       </c>
       <c r="E12" t="n">
-        <v>18.8994</v>
+        <v>20.2045</v>
       </c>
       <c r="F12" t="n">
         <v>-3.8539</v>
@@ -1390,13 +1390,13 @@
         <v>7.2841</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2835</v>
+        <v>3.5883</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0887</v>
+        <v>4.3936</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8051999999999999</v>
+        <v>-0.8052999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>4.0863</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6104</v>
+        <v>1.1397</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9127</v>
+        <v>1.2698</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3023</v>
+        <v>-0.1301</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0481</v>
@@ -1468,13 +1468,13 @@
         <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0321</v>
+        <v>0.5614</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5435</v>
+        <v>0.9006</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5115</v>
+        <v>-0.3392</v>
       </c>
       <c r="V13" t="n">
         <v>1.8751</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3316</v>
+        <v>1.0292</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3325</v>
+        <v>3.1182</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0009</v>
+        <v>-2.089</v>
       </c>
       <c r="G14" t="n">
         <v>0.2289</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4097</v>
+        <v>-0.7121</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2948</v>
+        <v>0.0805</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7045</v>
+        <v>-0.7926</v>
       </c>
       <c r="V14" t="n">
         <v>0.888</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0408</v>
+        <v>-0.0566</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4739</v>
+        <v>1.0856</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5148</v>
+        <v>-1.1422</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9231</v>
+        <v>1.0432</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6463</v>
+        <v>0.4538</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2768</v>
+        <v>0.5895</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5105</v>
+        <v>3.3295</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5889</v>
+        <v>1.9971</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0784</v>
+        <v>1.3324</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4126</v>
+        <v>-2.2863</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0574</v>
+        <v>-1.5434</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3551</v>
+        <v>-0.7429</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7674</v>
+        <v>-0.3704</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9844000000000001</v>
+        <v>-0.4957</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7829</v>
+        <v>0.1253</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5095</v>
+        <v>-0.9376</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5095</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0424</v>
+        <v>-0.4377</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9784</v>
+        <v>1.958</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0209</v>
+        <v>-2.3957</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0432</v>
+        <v>-0.1283</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4538</v>
+        <v>-1.6289</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5895</v>
+        <v>1.5006</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3295</v>
+        <v>2.0437</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9971</v>
+        <v>0.2982</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3324</v>
+        <v>1.7455</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2863</v>
+        <v>-2.172</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5434</v>
+        <v>-1.9271</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7429</v>
+        <v>-0.2449</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3562</v>
+        <v>-0.3192</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6029</v>
+        <v>-0.0857</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2467</v>
+        <v>-0.2335</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9376</v>
+        <v>-1.447</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>-1.447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0489</v>
+        <v>-1.0845</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6365</v>
+        <v>-0.2762</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6854</v>
+        <v>-0.8083</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1283</v>
+        <v>-1.9231</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6289</v>
+        <v>-1.6463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5006</v>
+        <v>-0.2768</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0437</v>
+        <v>-0.5105</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2982</v>
+        <v>-0.5889</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7455</v>
+        <v>0.0784</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.172</v>
+        <v>-1.4126</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9271</v>
+        <v>-1.0574</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2449</v>
+        <v>-0.3551</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9303</v>
+        <v>0.7237</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4071</v>
+        <v>0.2343</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5232</v>
+        <v>0.4893</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.447</v>
+        <v>-0.5095</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.447</v>
+        <v>-0.5095</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8628</v>
+        <v>-2.4826</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1338</v>
+        <v>-0.8123</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.729</v>
+        <v>-1.6703</v>
       </c>
       <c r="G19" t="n">
         <v>-3.2777</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4176</v>
+        <v>-0.0374</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3014</v>
+        <v>0.02</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1161</v>
+        <v>-0.0574</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3205</v>
+        <v>-2.6333</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.597</v>
+        <v>0.5783</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7236</v>
+        <v>-3.2116</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8054</v>
+        <v>1.0857</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1899</v>
+        <v>-0.4818</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3845</v>
+        <v>1.5675</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0784</v>
+        <v>2.3351</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7446</v>
+        <v>0.6288</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6662</v>
+        <v>1.7063</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.727</v>
+        <v>-1.2494</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4453</v>
+        <v>-1.1106</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2817</v>
+        <v>-0.1388</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0157</v>
+        <v>-0.4396</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2296</v>
+        <v>0.3244</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2453</v>
+        <v>-0.7639</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7076</v>
+        <v>-2.0308</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.0308</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.404</v>
+        <v>-2.8841</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0425</v>
+        <v>-2.597</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4465</v>
+        <v>-0.2871</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0857</v>
+        <v>-2.8054</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4818</v>
+        <v>-3.1899</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5675</v>
+        <v>0.3845</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3351</v>
+        <v>-1.0784</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6288</v>
+        <v>-1.7446</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7063</v>
+        <v>0.6662</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2494</v>
+        <v>-1.727</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1106</v>
+        <v>-1.4453</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1388</v>
+        <v>-0.2817</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2102</v>
+        <v>0.4208</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2114</v>
+        <v>0.2296</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9988</v>
+        <v>0.1912</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0308</v>
+        <v>-0.7076</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4468</v>
+        <v>-3.1483</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.271</v>
+        <v>-0.0567</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1758</v>
+        <v>-3.0917</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3953</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0921</v>
+        <v>-0.7937</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7705</v>
+        <v>-0.5562</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3216</v>
+        <v>-0.2374</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8992</v>
+        <v>-3.8508</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5987</v>
+        <v>-0.4916</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3005</v>
+        <v>-3.3592</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5777</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7287</v>
+        <v>-0.6803</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0314</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6974</v>
+        <v>-0.7561</v>
       </c>
       <c r="V23" t="n">
         <v>-0.0495</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.0458</v>
+        <v>-14.3314</v>
       </c>
       <c r="E24" t="n">
-        <v>3.853600000000001</v>
+        <v>3.853699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.8997</v>
+        <v>-18.1852</v>
       </c>
       <c r="G24" t="n">
         <v>-11.7978</v>
@@ -2296,16 +2296,16 @@
         <v>-13.5938</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7961</v>
+        <v>1.796100000000001</v>
       </c>
       <c r="J24" t="n">
         <v>7.431699999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5738</v>
+        <v>1.573800000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>5.8578</v>
+        <v>5.857799999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-19.2293</v>
@@ -2314,28 +2314,28 @@
         <v>-15.1678</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.061599999999999</v>
+        <v>-4.0616</v>
       </c>
       <c r="P24" t="n">
-        <v>3.121799999999999</v>
+        <v>3.1218</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.2842</v>
+        <v>-7.284199999999998</v>
       </c>
       <c r="R24" t="n">
         <v>10.406</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.283399999999999</v>
+        <v>-1.5692</v>
       </c>
       <c r="T24" t="n">
         <v>0.8052</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.0888</v>
+        <v>-2.3743</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.0864</v>
+        <v>-4.086400000000001</v>
       </c>
       <c r="W24" t="n">
         <v>2.9011</v>
